--- a/Cardamyst_Coverage_Tracker Jan 2026.xlsx
+++ b/Cardamyst_Coverage_Tracker Jan 2026.xlsx
@@ -555,7 +555,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
@@ -689,7 +689,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -780,7 +780,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -813,7 +813,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -926,7 +926,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
@@ -1020,7 +1020,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -1111,7 +1111,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -1144,7 +1144,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -1489,10 +1489,10 @@
         <v>187209834</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>16150884</v>
+        <v>7034139</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>0.0863</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
@@ -1552,10 +1552,10 @@
         <v>73287278</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>4918763</v>
+        <v>0</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>0.06709999999999999</v>
+        <v>0</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
@@ -1573,10 +1573,10 @@
         <v>314775891</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>21069647</v>
+        <v>7034139</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>0.0669</v>
+        <v>0.0223</v>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
@@ -1636,180 +1636,180 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield Massachusetts Standard 3-tier</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Employer</t>
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>1004502</v>
+        <v>185337</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>(NC)</t>
+          <t>(T3)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Molina Healthcare Washington</t>
+          <t>UnitedHealthcare Community Plan Essential</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>Managed Medicaid</t>
+          <t>HIX-Medicaid</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>772439</v>
+        <v>174217</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>(NC)  (PA)</t>
+          <t>(T3)  (PA)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Florida Blue Open</t>
+          <t>CHI Franciscan</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Employer</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>761441</v>
+        <v>135877</v>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>(NC)</t>
+          <t>(T3)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Florida Blue Care Choices 7-Tier Silver</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>HIX</t>
+          <t>Employer</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>746709</v>
+        <v>118347</v>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>(NC)</t>
+          <t>(T3)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Community Health Plan</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Managed Medicaid</t>
+          <t>Employer</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>686327</v>
+        <v>105536</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>(NC)  (PA)</t>
+          <t>(T3)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Cigna Performance 3-Tier</t>
+          <t>General Electric</t>
         </is>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Employer</t>
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>629275</v>
+        <v>98194</v>
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>(NC)</t>
+          <t>(T3)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield MN Medicaid</t>
+          <t>State of Michigan</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Managed Medicaid</t>
+          <t>Employer</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>364591</v>
+        <v>95690</v>
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>(NC)  (PA)</t>
+          <t>(T3)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Florida Blue Care Choices 7-Tier Bronze</t>
+          <t>Weis Markets</t>
         </is>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>HIX</t>
+          <t>Employer</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>363097</v>
+        <v>40010</v>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>(NC)</t>
+          <t>(T3)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>CareSource (GA)</t>
+          <t>Smithfield Foods</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>Managed Medicaid</t>
+          <t>Employer</t>
         </is>
       </c>
       <c r="C25" s="18" t="n">
-        <v>306599</v>
+        <v>23040</v>
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>(NC)  (PA)</t>
+          <t>(T3)</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>0.0863</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="C7" s="23" t="n"/>
       <c r="D7" s="23" t="n"/>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="B9" s="25" t="n">
-        <v>16150884</v>
+        <v>7034139</v>
       </c>
       <c r="C9" s="25" t="n"/>
       <c r="D9" s="25" t="n"/>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>0.06709999999999999</v>
+        <v>0</v>
       </c>
       <c r="C19" s="23" t="n"/>
       <c r="D19" s="23" t="n"/>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="B20" s="25" t="n">
-        <v>4918763</v>
+        <v>0</v>
       </c>
       <c r="C20" s="25" t="n"/>
       <c r="D20" s="25" t="n"/>
@@ -2797,16 +2797,16 @@
         <v>0</v>
       </c>
       <c r="C4" s="33" t="n">
-        <v>0.0863</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="D4" s="33" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="33" t="n">
-        <v>0.06709999999999999</v>
+        <v>0</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>0.0669</v>
+        <v>0.0223</v>
       </c>
     </row>
     <row r="5">
@@ -3256,7 +3256,7 @@
     <row r="2">
       <c r="A2" s="35" t="inlineStr">
         <is>
-          <t>Total: 10 plans covering 21,069,647 lives</t>
+          <t>Total: 10 plans covering 7,034,139 lives</t>
         </is>
       </c>
     </row>
@@ -3326,21 +3326,21 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield Massachusetts Standard 3-tier</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Employer</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="7" t="n">
-        <v>1004502</v>
+        <v>185337</v>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>(NC)</t>
+          <t>(T3)</t>
         </is>
       </c>
     </row>
@@ -3352,21 +3352,21 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Molina Healthcare Washington</t>
+          <t>UnitedHealthcare Community Plan Essential</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Managed Medicaid</t>
+          <t>HIX-Medicaid</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="7" t="n">
-        <v>772439</v>
+        <v>174217</v>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>(NC)  (PA)</t>
+          <t>(T3)  (PA)</t>
         </is>
       </c>
     </row>
@@ -3378,21 +3378,21 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Florida Blue Open</t>
+          <t>CHI Franciscan</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Employer</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="7" t="n">
-        <v>761441</v>
+        <v>135877</v>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>(NC)</t>
+          <t>(T3)</t>
         </is>
       </c>
     </row>
@@ -3404,47 +3404,47 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Florida Blue Care Choices 7-Tier Silver</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>HIX</t>
+          <t>Employer</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr"/>
       <c r="E9" s="7" t="n">
-        <v>746709</v>
+        <v>118347</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>(NC)</t>
+          <t>(T3)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Medicaid</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Community Health Plan</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Managed Medicaid</t>
+          <t>Employer</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr"/>
       <c r="E10" s="7" t="n">
-        <v>686327</v>
+        <v>105536</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>(NC)  (PA)</t>
+          <t>(T3)</t>
         </is>
       </c>
     </row>
@@ -3456,47 +3456,47 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Cigna Performance 3-Tier</t>
+          <t>General Electric</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Employer</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="7" t="n">
-        <v>629275</v>
+        <v>98194</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>(NC)</t>
+          <t>(T3)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Medicaid</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield MN Medicaid</t>
+          <t>State of Michigan</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Managed Medicaid</t>
+          <t>Employer</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr"/>
       <c r="E12" s="7" t="n">
-        <v>364591</v>
+        <v>95690</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>(NC)  (PA)</t>
+          <t>(T3)</t>
         </is>
       </c>
     </row>
@@ -3508,47 +3508,47 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Florida Blue Care Choices 7-Tier Bronze</t>
+          <t>Weis Markets</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>HIX</t>
+          <t>Employer</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr"/>
       <c r="E13" s="7" t="n">
-        <v>363097</v>
+        <v>40010</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>(NC)</t>
+          <t>(T3)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Medicaid</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>CareSource (GA)</t>
+          <t>Smithfield Foods</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Managed Medicaid</t>
+          <t>Employer</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr"/>
       <c r="E14" s="7" t="n">
-        <v>306599</v>
+        <v>23040</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>(NC)  (PA)</t>
+          <t>(T3)</t>
         </is>
       </c>
     </row>
